--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128167446</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90863</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Knutgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>602564</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6490189</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90863</v>
+        <v>90869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90869</v>
+        <v>90961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90961</v>
+        <v>90973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128167446</v>
       </c>
       <c r="B3" t="n">
-        <v>91003</v>
+        <v>91013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128167545</v>
+        <v>128167228</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602421</v>
+        <v>602561</v>
       </c>
       <c r="R2" t="n">
-        <v>6490143</v>
+        <v>6490171</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,21 +780,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128167446</v>
+        <v>128167249</v>
       </c>
       <c r="B3" t="n">
-        <v>91013</v>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,48 +807,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5741</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knutgärdet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602564</v>
+        <v>602561</v>
       </c>
       <c r="R3" t="n">
-        <v>6490189</v>
+        <v>6490171</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +895,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -928,6 +910,494 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128167186</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knutgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602578</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6490219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128167415</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knutgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602561</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6490171</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128167446</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knutgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602564</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6490189</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128167545</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knutgärdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>602421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6490143</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21536-2025 artfynd.xlsx
+++ b/artfynd/A 21536-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -809,6 +814,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167545</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,8 +1428,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128167446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>